--- a/document/TaskMan_タスク一覧表示画面_画面設計書.xlsx
+++ b/document/TaskMan_タスク一覧表示画面_画面設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER112\Desktop\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E85512-25BF-4B8C-BA2A-E4F304991E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF038FD-8DE8-4015-BD8F-BD3D4B40320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -37,30 +37,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="123">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -129,9 +107,6 @@
   </si>
   <si>
     <t>詳細クラス図</t>
-  </si>
-  <si>
-    <t>画面設計書</t>
   </si>
   <si>
     <t>画面名称</t>
@@ -289,10 +264,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task_edit_form.jsp  |   task_deleting_confirmation.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>なし</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -309,10 +280,6 @@
   </si>
   <si>
     <t>label</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>tblTaskId</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -500,29 +467,39 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク編集画面へ遷移するボタン</t>
-    <rPh sb="3" eb="7">
-      <t>ヘンシュウガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
+    <t>画面設+A1:J24計書</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク削除確認画面へ遷移するボタン</t>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センイ</t>
-    </rPh>
+    <t>ltblTaskId</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>rdoTaskSelect</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>radio</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクを編集画面へ遷移</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクを削除確認画面へ遷移</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集・削除対象を1件選択する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-edit-form.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1305,7 +1282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1621,9 +1598,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1642,12 +1616,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1655,6 +1623,99 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1674,68 +1735,58 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>169707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1011403</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>928091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD2564A5-2013-C3F9-0DD1-6DA9A8EEB67A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="353786" y="1734528"/>
+          <a:ext cx="7257081" cy="2391242"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7143,7 +7194,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1005"/>
+  <dimension ref="A1:J1006"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7153,18 +7204,18 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
+        <v>114</v>
+      </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
       <c r="D1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
+      <c r="E1" s="132"/>
       <c r="F1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="132"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7176,502 +7227,523 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="116"/>
       <c r="D2" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="114"/>
+      <c r="F2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
+      <c r="G2" s="114"/>
       <c r="H2" s="70">
         <v>46176</v>
       </c>
       <c r="I2" s="72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="139"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="137"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="142"/>
+      <c r="J4" s="140"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="61"/>
+        <v>23</v>
+      </c>
+      <c r="B5" s="133"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="129"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="46"/>
+        <v>24</v>
+      </c>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="110"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="62" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="64"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="122"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="65"/>
+      <c r="A8" s="123"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="65"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="125"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="65"/>
+      <c r="A10" s="123"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="65"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="125"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="65"/>
+      <c r="A12" s="123"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="1:10" ht="75.75" customHeight="1">
-      <c r="A13" s="112"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="105"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="111"/>
+        <v>25</v>
+      </c>
+      <c r="B14" s="109"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="110"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="109"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="15" t="s">
-        <v>28</v>
-      </c>
       <c r="J15" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="109"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="H16" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="110"/>
-      <c r="J16" s="111"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="110"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="112"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>75</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
       <c r="H17" s="45"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="108"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
+        <v>115</v>
+      </c>
+      <c r="B18" s="112"/>
+      <c r="C18" s="113"/>
       <c r="D18" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H18" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
+        <v>106</v>
+      </c>
+      <c r="I18" s="107"/>
+      <c r="J18" s="108"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
+        <v>74</v>
+      </c>
+      <c r="B19" s="112"/>
+      <c r="C19" s="113"/>
       <c r="D19" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H19" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="I19" s="108"/>
-      <c r="J19" s="109"/>
+        <v>107</v>
+      </c>
+      <c r="I19" s="107"/>
+      <c r="J19" s="108"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
+        <v>75</v>
+      </c>
+      <c r="B20" s="112"/>
+      <c r="C20" s="113"/>
       <c r="D20" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H20" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="108"/>
-      <c r="J20" s="109"/>
+        <v>108</v>
+      </c>
+      <c r="I20" s="107"/>
+      <c r="J20" s="108"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
+        <v>76</v>
+      </c>
+      <c r="B21" s="112"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H21" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="108"/>
-      <c r="J21" s="109"/>
+        <v>109</v>
+      </c>
+      <c r="I21" s="107"/>
+      <c r="J21" s="108"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
+        <v>77</v>
+      </c>
+      <c r="B22" s="112"/>
+      <c r="C22" s="113"/>
       <c r="D22" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H22" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="108"/>
-      <c r="J22" s="109"/>
+        <v>110</v>
+      </c>
+      <c r="I22" s="107"/>
+      <c r="J22" s="108"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
+        <v>78</v>
+      </c>
+      <c r="B23" s="112"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="114" t="s">
-        <v>99</v>
+        <v>73</v>
+      </c>
+      <c r="F23" s="111" t="s">
+        <v>96</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H23" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="108"/>
-      <c r="J23" s="109"/>
+        <v>111</v>
+      </c>
+      <c r="I23" s="107"/>
+      <c r="J23" s="108"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
       <c r="A24" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="115"/>
-      <c r="C24" s="116"/>
+        <v>79</v>
+      </c>
+      <c r="B24" s="112"/>
+      <c r="C24" s="113"/>
       <c r="D24" s="38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="114" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="111" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>103</v>
-      </c>
       <c r="H24" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="I24" s="108"/>
-      <c r="J24" s="109"/>
+        <v>112</v>
+      </c>
+      <c r="I24" s="107"/>
+      <c r="J24" s="108"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
       <c r="A25" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="115"/>
-      <c r="C25" s="116"/>
+        <v>80</v>
+      </c>
+      <c r="B25" s="112"/>
+      <c r="C25" s="113"/>
       <c r="D25" s="38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="114" t="s">
-        <v>102</v>
+        <v>73</v>
+      </c>
+      <c r="F25" s="111" t="s">
+        <v>99</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H25" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="I25" s="108"/>
-      <c r="J25" s="109"/>
+        <v>113</v>
+      </c>
+      <c r="I25" s="107"/>
+      <c r="J25" s="108"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="115"/>
-      <c r="C26" s="116"/>
+        <v>81</v>
+      </c>
+      <c r="B26" s="112"/>
+      <c r="C26" s="113"/>
       <c r="D26" s="38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="114" t="s">
-        <v>101</v>
+        <v>73</v>
+      </c>
+      <c r="F26" s="111" t="s">
+        <v>98</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="I26" s="108"/>
-      <c r="J26" s="109"/>
+        <v>113</v>
+      </c>
+      <c r="I26" s="107"/>
+      <c r="J26" s="108"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
       <c r="A27" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" s="107"/>
+      <c r="J27" s="108"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="112"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="I28" s="107"/>
+      <c r="J28" s="108"/>
+    </row>
+    <row r="29" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
+      <c r="A29" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="130"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="115"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="I27" s="108"/>
-      <c r="J27" s="109"/>
-    </row>
-    <row r="28" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A28" s="57" t="s">
+      <c r="E29" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H28" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28" s="106"/>
-      <c r="J28" s="107"/>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="105"/>
+      <c r="J29" s="106"/>
+    </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8648,14 +8720,19 @@
     <row r="1003" ht="12.75" customHeight="1"/>
     <row r="1004" ht="12.75" customHeight="1"/>
     <row r="1005" ht="12.75" customHeight="1"/>
+    <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="43">
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="F2:G4"/>
@@ -8666,7 +8743,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
@@ -8678,7 +8754,6 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H28:J28"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:C20"/>
@@ -8695,6 +8770,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8710,7 +8786,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
       <c r="A1" s="82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -8810,7 +8886,7 @@
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
@@ -8818,7 +8894,7 @@
       <c r="E5" s="54"/>
       <c r="F5" s="55"/>
       <c r="G5" s="80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="54"/>
@@ -8836,7 +8912,7 @@
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
@@ -8862,7 +8938,7 @@
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="43"/>
       <c r="C7" s="43"/>
@@ -8870,7 +8946,7 @@
       <c r="E7" s="43"/>
       <c r="F7" s="44"/>
       <c r="G7" s="45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7" s="43"/>
       <c r="I7" s="43"/>
@@ -8912,11 +8988,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -8946,7 +9022,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -8976,7 +9052,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -9006,7 +9082,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -9036,7 +9112,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -9084,44 +9160,44 @@
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
       <c r="A15" s="59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="44"/>
       <c r="C15" s="102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="44"/>
       <c r="J15" s="66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K15" s="44"/>
       <c r="L15" s="66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M15" s="43"/>
       <c r="N15" s="44"/>
       <c r="O15" s="66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P15" s="43"/>
       <c r="Q15" s="44"/>
       <c r="R15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="S15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>53</v>
-      </c>
-      <c r="T15" s="32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
@@ -9130,29 +9206,29 @@
       </c>
       <c r="B16" s="44"/>
       <c r="C16" s="96" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="43"/>
       <c r="I16" s="44"/>
       <c r="J16" s="101" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K16" s="44"/>
       <c r="L16" s="99" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M16" s="43"/>
       <c r="N16" s="44"/>
       <c r="O16" s="99" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P16" s="43"/>
       <c r="Q16" s="44"/>
@@ -9172,29 +9248,29 @@
       </c>
       <c r="B17" s="44"/>
       <c r="C17" s="96" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="101" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="44"/>
       <c r="J17" s="101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K17" s="44"/>
       <c r="L17" s="99" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M17" s="43"/>
       <c r="N17" s="44"/>
       <c r="O17" s="99" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P17" s="43"/>
       <c r="Q17" s="44"/>

--- a/document/TaskMan_タスク一覧表示画面_画面設計書.xlsx
+++ b/document/TaskMan_タスク一覧表示画面_画面設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER112\Desktop\プロジェクト演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E85512-25BF-4B8C-BA2A-E4F304991E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A47335-42D2-45E4-A654-2047A9581DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="116">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -233,38 +233,6 @@
   <si>
     <t xml:space="preserve">正常系
 </t>
-  </si>
-  <si>
-    <t>URLアクセス</t>
-  </si>
-  <si>
-    <t>なし</t>
-  </si>
-  <si>
-    <t>http://localhost:8080/ans1101/login.html　へアクセスする</t>
-  </si>
-  <si>
-    <t>ログイン画面へ遷移する</t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>異常系</t>
-  </si>
-  <si>
-    <t>ユーザIDがDBに登録されていないときのログインボタン動作</t>
-  </si>
-  <si>
-    <t>・ユーザID：999999
-・パスワード：root</t>
-  </si>
-  <si>
-    <t>ログインするボタンを押下する</t>
-  </si>
-  <si>
-    <t>エラー画面へ遷移する
-エラーの原因がユーザ名が未入力である旨通知する</t>
   </si>
   <si>
     <t>TaskMan</t>
@@ -525,6 +493,104 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>ログアウト画面の表示</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>アプリケーションが起動している</t>
+  </si>
+  <si>
+    <t>ログアウト画面が表示される。
+画面上部に「お疲れ様でした」の文言のあとにログイン中のユーザー名が表示される。
+画面下部に「ログイン画面へ」ボタンが表示される。</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ブラウザでlogout.jspを表示する</t>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン画面への遷移</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>「ログイン画面へ」ボタンを押下する</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン画面に遷移する。</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -533,7 +599,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -551,6 +617,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -595,6 +662,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -610,7 +684,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="60">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -1301,11 +1375,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1423,172 +1512,223 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1597,64 +1737,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1945,85 +2046,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2043,46 +2144,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="79" t="s">
+      <c r="E8" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="75" t="s">
+      <c r="G13" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="44"/>
-      <c r="I13" s="75" t="s">
+      <c r="H13" s="69"/>
+      <c r="I13" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="43"/>
-      <c r="K13" s="44"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="75"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="44"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="75"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="44"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="69"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2091,13 +2192,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="76" t="s">
+      <c r="G17" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3111,19 +3212,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="62"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3135,168 +3236,168 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="46"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="46"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="103"/>
+      <c r="B10" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="46"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91" t="s">
+      <c r="A11" s="104"/>
+      <c r="B11" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="46"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="46"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4287,17 +4388,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4306,14 +4404,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4332,19 +4433,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="62"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4356,40 +4457,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5745,19 +5846,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="62"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5769,40 +5870,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7152,19 +7253,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="62"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7176,205 +7277,205 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="67" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="47"/>
+      <c r="F2" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="47"/>
+      <c r="H2" s="50">
         <v>46176</v>
       </c>
-      <c r="I2" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="73"/>
+      <c r="I2" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="62" t="e" vm="1">
+      <c r="A7" s="73" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="64"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="75"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="65"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="65"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="76"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="65"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="76"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="65"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="76"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="65"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="76"/>
     </row>
     <row r="13" spans="1:10" ht="75.75" customHeight="1">
-      <c r="A13" s="112"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="105"/>
+      <c r="A13" s="77"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="111"/>
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="81"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -7387,289 +7488,289 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="66" t="s">
+      <c r="H16" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="110"/>
-      <c r="J16" s="111"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="81"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
+      <c r="A17" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
       <c r="D17" s="17" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="45"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" s="44"/>
+      <c r="J18" s="45"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="68"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="17" t="s">
+      <c r="E19" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="44"/>
+      <c r="J19" s="45"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="44"/>
+      <c r="J20" s="45"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="18" t="s">
+      <c r="G21" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="44"/>
+      <c r="J21" s="45"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="18" t="s">
+      <c r="I22" s="44"/>
+      <c r="J22" s="45"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="44"/>
+      <c r="J23" s="45"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="44"/>
+      <c r="J24" s="45"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="44"/>
+      <c r="J25" s="45"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="44"/>
+      <c r="J27" s="45"/>
+    </row>
+    <row r="28" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
+      <c r="A28" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="I19" s="108"/>
-      <c r="J19" s="109"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="108"/>
-      <c r="J20" s="109"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="18" t="s">
+      <c r="B28" s="65"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H21" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="108"/>
-      <c r="J21" s="109"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="18" t="s">
+      <c r="E28" s="19" t="s">
         <v>98</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="108"/>
-      <c r="J22" s="109"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="114" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="108"/>
-      <c r="J23" s="109"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="115"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="114" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="I24" s="108"/>
-      <c r="J24" s="109"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="115"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="114" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="I25" s="108"/>
-      <c r="J25" s="109"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="115"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="114" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="I26" s="108"/>
-      <c r="J26" s="109"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="115"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="I27" s="108"/>
-      <c r="J27" s="109"/>
-    </row>
-    <row r="28" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A28" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>108</v>
       </c>
       <c r="F28" s="20"/>
       <c r="G28" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H28" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28" s="106"/>
-      <c r="J28" s="107"/>
+        <v>97</v>
+      </c>
+      <c r="H28" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="I28" s="84"/>
+      <c r="J28" s="85"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8650,19 +8751,18 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8679,18 +8779,19 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8700,7 +8801,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z988"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="2.85546875" customWidth="1"/>
@@ -8709,182 +8810,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="56" t="s">
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="56" t="s">
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="56" t="s">
+      <c r="P1" s="62"/>
+      <c r="Q1" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="55"/>
-      <c r="S1" s="56" t="s">
+      <c r="R1" s="62"/>
+      <c r="S1" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="61"/>
+      <c r="T1" s="71"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="64"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="120">
+        <v>46177</v>
+      </c>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="75"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="65"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="76"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="103"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="111"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="80" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="71"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="46"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="45" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="46"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="68"/>
+      <c r="T7" s="72"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9083,37 +9190,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="102" t="s">
+      <c r="B15" s="69"/>
+      <c r="C15" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="66" t="s">
+      <c r="D15" s="69"/>
+      <c r="E15" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="66" t="s">
+      <c r="F15" s="69"/>
+      <c r="G15" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="66" t="s">
+      <c r="H15" s="68"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="44"/>
-      <c r="L15" s="66" t="s">
+      <c r="K15" s="69"/>
+      <c r="L15" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="43"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="66" t="s">
+      <c r="M15" s="68"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="44"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="69"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -9124,38 +9231,38 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="95">
+    <row r="16" spans="1:26" ht="134.25" customHeight="1">
+      <c r="A16" s="112">
         <v>1</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="96" t="s">
+      <c r="B16" s="69"/>
+      <c r="C16" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="96" t="s">
+      <c r="D16" s="69"/>
+      <c r="E16" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="101" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="101" t="s">
-        <v>58</v>
-      </c>
-      <c r="K16" s="44"/>
-      <c r="L16" s="99" t="s">
-        <v>59</v>
-      </c>
-      <c r="M16" s="43"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="44"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="107" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="68"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="117" t="s">
+        <v>110</v>
+      </c>
+      <c r="K16" s="118"/>
+      <c r="L16" s="119" t="s">
+        <v>112</v>
+      </c>
+      <c r="M16" s="118"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="119" t="s">
+        <v>111</v>
+      </c>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -9167,37 +9274,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="95">
+      <c r="A17" s="112">
         <v>2</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="96" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="96" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="69"/>
+      <c r="E17" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="69"/>
+      <c r="G17" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="68"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="44"/>
-      <c r="G17" s="101" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="K17" s="44"/>
-      <c r="L17" s="99" t="s">
-        <v>65</v>
-      </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="99" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="44"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="109" t="s">
+        <v>114</v>
+      </c>
+      <c r="M17" s="68"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="109" t="s">
+        <v>115</v>
+      </c>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="69"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -9209,23 +9316,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="95"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="99"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="44"/>
+      <c r="A18" s="112"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="109"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="69"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -9237,26 +9344,26 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="95"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="101"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
+      <c r="A19" s="115"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="110"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="37"/>
       <c r="U19" s="35"/>
       <c r="V19" s="35"/>
       <c r="W19" s="35"/>
@@ -9265,374 +9372,50 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="95"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="101"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="101"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="99"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="95"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
-    </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="95"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="101"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="99"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
-    </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="95"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="101"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="101"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="99"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
-    </row>
-    <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="95"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="101"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="99"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-    </row>
-    <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="95"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-    </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="95"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-    </row>
-    <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="95"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="99"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
-    </row>
-    <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="95"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="101"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
-    </row>
-    <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="95"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="101"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="99"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="99"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
-    </row>
-    <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="95"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
-    </row>
-    <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="36"/>
-      <c r="S31" s="36"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-    </row>
-    <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="36" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="37" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="38" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="39" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="40" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="41" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="42" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="43" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="44" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="45" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="46" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="47" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="48" spans="4:10" ht="12.75" customHeight="1"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
     <row r="49" ht="12.75" customHeight="1"/>
     <row r="50" ht="12.75" customHeight="1"/>
     <row r="51" ht="12.75" customHeight="1"/>
@@ -10573,65 +10356,37 @@
     <row r="986" ht="12.75" customHeight="1"/>
     <row r="987" ht="12.75" customHeight="1"/>
     <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
+  <mergeCells count="52">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="K2:N4"/>
     <mergeCell ref="O2:P4"/>
     <mergeCell ref="Q2:R4"/>
@@ -10643,86 +10398,18 @@
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="G2:J4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
